--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/font_size_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/font_size_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>19.5</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>4.02</v>
       </c>
     </row>
   </sheetData>
